--- a/config/xlsx/home_meridians.xlsx
+++ b/config/xlsx/home_meridians.xlsx
@@ -1,51 +1,437 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="home_meridians" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="home_meridians" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>acupoints</t>
+  </si>
+  <si>
+    <t>qi_cost</t>
+  </si>
+  <si>
+    <t>acupoint_rewards</t>
+  </si>
+  <si>
+    <t>circulation_rewards</t>
+  </si>
+  <si>
+    <t>练气期·经脉初开</t>
+  </si>
+  <si>
+    <t>筑基期·经脉贯通</t>
+  </si>
+  <si>
+    <t>金丹期·经脉大成</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -54,99 +440,335 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,111 +1051,91 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="22.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="32.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>acupoints</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>qi_cost</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>acupoint_rewards</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>circulation_rewards</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>练气期·经脉初开</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="3">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>筑基期·经脉贯通</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="3">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>金丹期·经脉大成</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="2">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3">
         <v>20</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="3">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/config/xlsx/home_meridians.xlsx
+++ b/config/xlsx/home_meridians.xlsx
@@ -467,12 +467,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>acupoint_rewards</t>
+          <t>acupoint_exp</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>circulation_rewards</t>
+          <t>circulation_exp</t>
         </is>
       </c>
     </row>
@@ -486,17 +486,13 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -509,17 +505,13 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -532,17 +524,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>72</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -555,17 +543,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>87</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -578,17 +562,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>102</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -601,17 +581,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>114</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -624,17 +600,13 @@
         <v>28</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>129</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -647,17 +619,13 @@
         <v>31</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>144</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -670,17 +638,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>159</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -693,17 +657,13 @@
         <v>35</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>375</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -716,17 +676,13 @@
         <v>36</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>390</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -739,17 +695,13 @@
         <v>37</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>402</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -762,17 +714,13 @@
         <v>38</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>417</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -785,17 +733,13 @@
         <v>39</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>432</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -808,17 +752,13 @@
         <v>40</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>447</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -831,17 +771,13 @@
         <v>41</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>462</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -854,17 +790,13 @@
         <v>42</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>474</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -877,17 +809,13 @@
         <v>43</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>489</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -900,17 +828,13 @@
         <v>44</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>504</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -923,17 +847,13 @@
         <v>35</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>489</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -946,17 +866,13 @@
         <v>36</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>504</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -969,17 +885,13 @@
         <v>37</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>519</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -992,17 +904,13 @@
         <v>38</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>534</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1015,17 +923,13 @@
         <v>39</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>549</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1038,17 +942,13 @@
         <v>40</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>561</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1061,17 +961,13 @@
         <v>41</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>576</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1084,17 +980,13 @@
         <v>42</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>591</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -1107,17 +999,13 @@
         <v>43</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>606</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -1130,17 +1018,13 @@
         <v>44</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>621</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="31">
@@ -1153,17 +1037,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>633</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="32">
@@ -1176,17 +1056,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>648</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="33">
@@ -1199,17 +1075,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>663</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="34">
@@ -1222,17 +1094,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>226</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>678</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="35">
@@ -1245,17 +1113,13 @@
         <v>39</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>231</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>693</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="36">
@@ -1268,17 +1132,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>705</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="37">
@@ -1291,17 +1151,13 @@
         <v>41</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>720</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="38">
@@ -1314,17 +1170,13 @@
         <v>42</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>735</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="39">
@@ -1337,17 +1189,13 @@
         <v>43</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>750</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -1360,17 +1208,13 @@
         <v>44</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>765</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="41">
@@ -1383,17 +1227,13 @@
         <v>45</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>269</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>807</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="42">
@@ -1406,17 +1246,13 @@
         <v>46</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>822</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="43">
@@ -1429,17 +1265,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>837</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="44">
@@ -1452,17 +1284,13 @@
         <v>48</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>849</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="45">
@@ -1475,17 +1303,13 @@
         <v>49</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>864</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="46">
@@ -1498,17 +1322,13 @@
         <v>50</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>879</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="47">
@@ -1521,17 +1341,13 @@
         <v>51</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>894</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="48">
@@ -1544,17 +1360,13 @@
         <v>52</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>303</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>909</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="49">
@@ -1567,17 +1379,13 @@
         <v>53</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>307</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>921</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="50">
@@ -1590,17 +1398,13 @@
         <v>54</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>312</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>936</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="51">
@@ -1613,17 +1417,13 @@
         <v>45</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>346</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1038</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -1636,17 +1436,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>351</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1053</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="53">
@@ -1659,17 +1455,13 @@
         <v>47</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>355</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1065</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="54">
@@ -1682,17 +1474,13 @@
         <v>48</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1080</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="55">
@@ -1705,17 +1493,13 @@
         <v>49</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1095</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="56">
@@ -1728,17 +1512,13 @@
         <v>50</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>370</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1110</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="57">
@@ -1751,17 +1531,13 @@
         <v>51</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>375</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1125</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="58">
@@ -1774,17 +1550,13 @@
         <v>52</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>379</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1137</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="59">
@@ -1797,17 +1569,13 @@
         <v>53</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>384</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1152</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -1820,17 +1588,13 @@
         <v>54</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>389</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1167</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="61">
@@ -1843,17 +1607,13 @@
         <v>45</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>442</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1326</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="62">
@@ -1866,17 +1626,13 @@
         <v>46</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>447</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1341</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="63">
@@ -1889,17 +1645,13 @@
         <v>47</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>451</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1353</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="64">
@@ -1912,17 +1664,13 @@
         <v>48</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>456</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1368</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="65">
@@ -1935,17 +1683,13 @@
         <v>49</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>461</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1383</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>189</v>
       </c>
     </row>
     <row r="66">
@@ -1958,17 +1702,13 @@
         <v>50</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>466</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1398</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="67">
@@ -1981,17 +1721,13 @@
         <v>51</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>471</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1413</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="68">
@@ -2004,17 +1740,13 @@
         <v>52</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>475</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1425</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>214</v>
       </c>
     </row>
     <row r="69">
@@ -2027,17 +1759,13 @@
         <v>53</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1440</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="70">
@@ -2050,17 +1778,13 @@
         <v>54</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>485</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1455</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="71">
@@ -2073,17 +1797,13 @@
         <v>55</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>576</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1728</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>425</v>
       </c>
     </row>
     <row r="72">
@@ -2096,17 +1816,13 @@
         <v>56</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>581</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1743</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>408</v>
       </c>
     </row>
     <row r="73">
@@ -2119,17 +1835,13 @@
         <v>57</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>586</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1758</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>391</v>
       </c>
     </row>
     <row r="74">
@@ -2142,17 +1854,13 @@
         <v>58</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>591</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1773</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="75">
@@ -2165,17 +1873,13 @@
         <v>59</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>596</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1788</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="76">
@@ -2188,17 +1892,13 @@
         <v>60</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1800</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="77">
@@ -2211,17 +1911,13 @@
         <v>61</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>605</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1815</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="78">
@@ -2234,17 +1930,13 @@
         <v>62</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>610</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1830</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>430</v>
       </c>
     </row>
     <row r="79">
@@ -2257,17 +1949,13 @@
         <v>63</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>615</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1845</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>415</v>
       </c>
     </row>
     <row r="80">
@@ -2280,17 +1968,13 @@
         <v>64</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>620</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>1860</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="81">
@@ -2303,17 +1987,13 @@
         <v>55</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>749</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2247</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="82">
@@ -2326,17 +2006,13 @@
         <v>56</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>754</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2262</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="83">
@@ -2349,17 +2025,13 @@
         <v>57</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>759</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2277</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="84">
@@ -2372,17 +2044,13 @@
         <v>58</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>764</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2292</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="85">
@@ -2395,17 +2063,13 @@
         <v>59</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>768</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2304</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="86">
@@ -2418,17 +2082,13 @@
         <v>60</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>773</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2319</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>170</v>
       </c>
     </row>
     <row r="87">
@@ -2441,17 +2101,13 @@
         <v>61</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>778</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2334</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="88">
@@ -2464,17 +2120,13 @@
         <v>62</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>783</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2349</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="89">
@@ -2487,17 +2139,13 @@
         <v>63</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>788</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2364</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="90">
@@ -2510,17 +2158,13 @@
         <v>64</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>792</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2376</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="91">
@@ -2533,17 +2177,13 @@
         <v>55</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>961</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2883</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>435</v>
       </c>
     </row>
     <row r="92">
@@ -2556,17 +2196,13 @@
         <v>56</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>965</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2895</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>418</v>
       </c>
     </row>
     <row r="93">
@@ -2579,17 +2215,13 @@
         <v>57</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>970</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2910</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="94">
@@ -2602,17 +2234,13 @@
         <v>58</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>975</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2925</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="95">
@@ -2625,17 +2253,13 @@
         <v>59</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>980</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2940</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="96">
@@ -2648,17 +2272,13 @@
         <v>60</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>985</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2955</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>410</v>
       </c>
     </row>
     <row r="97">
@@ -2671,17 +2291,13 @@
         <v>61</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>989</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2967</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>394</v>
       </c>
     </row>
     <row r="98">
@@ -2694,17 +2310,13 @@
         <v>62</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>994</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2982</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>440</v>
       </c>
     </row>
     <row r="99">
@@ -2717,17 +2329,13 @@
         <v>63</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>999</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>2997</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>425</v>
       </c>
     </row>
     <row r="100">
@@ -2740,17 +2348,13 @@
         <v>64</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>1004</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3012</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>410</v>
       </c>
     </row>
     <row r="101">
@@ -2763,17 +2367,13 @@
         <v>65</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>1249</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3747</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>955</v>
       </c>
     </row>
     <row r="102">
@@ -2786,17 +2386,13 @@
         <v>66</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>1254</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3762</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>922</v>
       </c>
     </row>
     <row r="103">
@@ -2809,17 +2405,13 @@
         <v>67</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>1258</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3774</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>956</v>
       </c>
     </row>
     <row r="104">
@@ -2832,17 +2424,13 @@
         <v>68</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>1263</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3789</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>924</v>
       </c>
     </row>
     <row r="105">
@@ -2855,17 +2443,13 @@
         <v>69</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>1268</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3804</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>961</v>
       </c>
     </row>
     <row r="106">
@@ -2878,17 +2462,13 @@
         <v>70</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1273</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3819</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>930</v>
       </c>
     </row>
     <row r="107">
@@ -2901,17 +2481,13 @@
         <v>71</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>1278</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3834</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>899</v>
       </c>
     </row>
     <row r="108">
@@ -2924,17 +2500,13 @@
         <v>72</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>1282</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3846</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="109">
@@ -2947,17 +2519,13 @@
         <v>73</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>1287</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3861</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>910</v>
       </c>
     </row>
     <row r="110">
@@ -2970,17 +2538,13 @@
         <v>74</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>1292</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:15</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>4:0;3:100</t>
-        </is>
+        <v>3876</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>954</v>
       </c>
     </row>
   </sheetData>

--- a/config/xlsx/home_meridians.xlsx
+++ b/config/xlsx/home_meridians.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,2077 +476,2215 @@
           <t>circulation_exp</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acupoint_rewards</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>练气一层·周天</t>
+          <t>凡人·引气</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>[{"items":[{"id":12001,"count":1}],"tokens":[{"token":4,"amount":10},{"token":3,"amount":15}]},{"items":[{"id":17001,"count":1}],"tokens":[{"token":4,"amount":10}]},{"items":[{"id":16001,"count":1}],"tokens":[{"token":4,"amount":10}]}]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>练气二层·周天</t>
+          <t>练气一层·周天</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>练气三层·周天</t>
+          <t>练气二层·周天</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>练气四层·周天</t>
+          <t>练气三层·周天</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>练气五层·周天</t>
+          <t>练气四层·周天</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>47</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>练气六层·周天</t>
+          <t>练气五层·周天</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>练气七层·周天</t>
+          <t>练气六层·周天</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>练气八层·周天</t>
+          <t>练气七层·周天</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>121</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>练气九层·周天</t>
+          <t>练气八层·周天</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>160</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天1</t>
+          <t>练气九层·周天</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>375</v>
+        <v>159</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>25</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天2</t>
+          <t>筑基前期·周天1</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天3</t>
+          <t>筑基前期·周天2</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天4</t>
+          <t>筑基前期·周天3</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>22</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天5</t>
+          <t>筑基前期·周天4</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>21</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天6</t>
+          <t>筑基前期·周天5</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天7</t>
+          <t>筑基前期·周天6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>19</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天8</t>
+          <t>筑基前期·周天7</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天9</t>
+          <t>筑基前期·周天8</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>17</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>筑基前期·周天10</t>
+          <t>筑基前期·周天9</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>16</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天1</t>
+          <t>筑基前期·周天10</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天2</t>
+          <t>筑基中期·周天1</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天3</t>
+          <t>筑基中期·周天2</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>16</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天4</t>
+          <t>筑基中期·周天3</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>14</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天5</t>
+          <t>筑基中期·周天4</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天6</t>
+          <t>筑基中期·周天5</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天7</t>
+          <t>筑基中期·周天6</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天8</t>
+          <t>筑基中期·周天7</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天9</t>
+          <t>筑基中期·周天8</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>筑基中期·周天10</t>
+          <t>筑基中期·周天9</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天1</t>
+          <t>筑基中期·周天10</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>75</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天2</t>
+          <t>筑基后期·周天1</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天3</t>
+          <t>筑基后期·周天2</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>663</v>
+        <v>648</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天4</t>
+          <t>筑基后期·周天3</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>678</v>
+        <v>663</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>63</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天5</t>
+          <t>筑基后期·周天4</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天6</t>
+          <t>筑基后期·周天5</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>55</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天7</t>
+          <t>筑基后期·周天6</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天8</t>
+          <t>筑基后期·周天7</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>735</v>
+        <v>720</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>47</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天9</t>
+          <t>筑基后期·周天8</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>筑基后期·周天10</t>
+          <t>筑基后期·周天9</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>83</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天1</t>
+          <t>筑基后期·周天10</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>120</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天2</t>
+          <t>金丹前期·周天1</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天3</t>
+          <t>金丹前期·周天2</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>108</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天4</t>
+          <t>金丹前期·周天3</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>102</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天5</t>
+          <t>金丹前期·周天4</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>96</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天6</t>
+          <t>金丹前期·周天5</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>140</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天7</t>
+          <t>金丹前期·周天6</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>135</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天8</t>
+          <t>金丹前期·周天7</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>130</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天9</t>
+          <t>金丹前期·周天8</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>125</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>金丹前期·周天10</t>
+          <t>金丹前期·周天9</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>120</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天1</t>
+          <t>金丹前期·周天10</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1038</v>
+        <v>936</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>85</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天2</t>
+          <t>金丹中期·周天1</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>82</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天3</t>
+          <t>金丹中期·周天2</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>79</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天4</t>
+          <t>金丹中期·周天3</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>76</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天5</t>
+          <t>金丹中期·周天4</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>73</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天6</t>
+          <t>金丹中期·周天5</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1110</v>
+        <v>1095</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>70</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天7</t>
+          <t>金丹中期·周天6</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>67</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天8</t>
+          <t>金丹中期·周天7</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>64</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天9</t>
+          <t>金丹中期·周天8</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1152</v>
+        <v>1137</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>61</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>金丹中期·周天10</t>
+          <t>金丹中期·周天9</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1167</v>
+        <v>1152</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>58</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天1</t>
+          <t>金丹中期·周天10</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1326</v>
+        <v>1167</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>180</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天2</t>
+          <t>金丹后期·周天1</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1341</v>
+        <v>1326</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>10</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>170</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天3</t>
+          <t>金丹后期·周天2</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1353</v>
+        <v>1341</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>207</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天4</t>
+          <t>金丹后期·周天3</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1368</v>
+        <v>1353</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>198</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天5</t>
+          <t>金丹后期·周天4</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1383</v>
+        <v>1368</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>189</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天6</t>
+          <t>金丹后期·周天5</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1398</v>
+        <v>1383</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>180</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天7</t>
+          <t>金丹后期·周天6</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1413</v>
+        <v>1398</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>171</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天8</t>
+          <t>金丹后期·周天7</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1425</v>
+        <v>1413</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>214</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天9</t>
+          <t>金丹后期·周天8</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1440</v>
+        <v>1425</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>206</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>金丹后期·周天10</t>
+          <t>金丹后期·周天9</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1455</v>
+        <v>1440</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>8</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>198</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天1</t>
+          <t>金丹后期·周天10</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1728</v>
+        <v>1455</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天2</t>
+          <t>元婴前期·周天1</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>1743</v>
+        <v>1728</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>17</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>408</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天3</t>
+          <t>元婴前期·周天2</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>1758</v>
+        <v>1743</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>17</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>391</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天4</t>
+          <t>元婴前期·周天3</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1773</v>
+        <v>1758</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>432</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天5</t>
+          <t>元婴前期·周天4</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1788</v>
+        <v>1773</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>416</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天6</t>
+          <t>元婴前期·周天5</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1800</v>
+        <v>1788</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>400</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天7</t>
+          <t>元婴前期·周天6</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>1815</v>
+        <v>1800</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>384</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天8</t>
+          <t>元婴前期·周天7</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>1830</v>
+        <v>1815</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>430</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天9</t>
+          <t>元婴前期·周天8</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>1845</v>
+        <v>1830</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>15</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>415</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>元婴前期·周天10</t>
+          <t>元婴前期·周天9</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>1860</v>
+        <v>1845</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>15</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>400</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天1</t>
+          <t>元婴前期·周天10</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2247</v>
+        <v>1860</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>140</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天2</t>
+          <t>元婴中期·周天1</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2262</v>
+        <v>2247</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>134</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天3</t>
+          <t>元婴中期·周天2</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2277</v>
+        <v>2262</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>128</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天4</t>
+          <t>元婴中期·周天3</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2292</v>
+        <v>2277</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>122</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天5</t>
+          <t>元婴中期·周天4</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2304</v>
+        <v>2292</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>6</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>116</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天6</t>
+          <t>元婴中期·周天5</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2319</v>
+        <v>2304</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>170</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天7</t>
+          <t>元婴中期·周天6</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2334</v>
+        <v>2319</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>165</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天8</t>
+          <t>元婴中期·周天7</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2349</v>
+        <v>2334</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>160</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天9</t>
+          <t>元婴中期·周天8</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>155</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>元婴中期·周天10</t>
+          <t>元婴中期·周天9</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>2376</v>
+        <v>2364</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>150</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天1</t>
+          <t>元婴中期·周天10</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2883</v>
+        <v>2376</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>435</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天2</t>
+          <t>元婴后期·周天1</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2895</v>
+        <v>2883</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>17</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>418</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天3</t>
+          <t>元婴后期·周天2</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>2910</v>
+        <v>2895</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>17</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>401</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天4</t>
+          <t>元婴后期·周天3</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>2925</v>
+        <v>2910</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>17</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>384</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天5</t>
+          <t>元婴后期·周天4</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>2940</v>
+        <v>2925</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>426</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天6</t>
+          <t>元婴后期·周天5</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>2955</v>
+        <v>2940</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>410</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天7</t>
+          <t>元婴后期·周天6</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>2967</v>
+        <v>2955</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>16</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>394</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天8</t>
+          <t>元婴后期·周天7</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>2982</v>
+        <v>2967</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>440</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天9</t>
+          <t>元婴后期·周天8</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>2997</v>
+        <v>2982</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>15</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>元婴后期·周天10</t>
+          <t>元婴后期·周天9</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>3012</v>
+        <v>2997</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>15</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>410</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天1</t>
+          <t>元婴后期·周天10</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>3747</v>
+        <v>3012</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>955</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天2</t>
+          <t>化神前期·周天1</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>3762</v>
+        <v>3747</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>33</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>922</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天3</t>
+          <t>化神前期·周天2</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>3774</v>
+        <v>3762</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>956</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天4</t>
+          <t>化神前期·周天3</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>3789</v>
+        <v>3774</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>32</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>924</v>
-      </c>
+        <v>956</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天5</t>
+          <t>化神前期·周天4</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>3804</v>
+        <v>3789</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>961</v>
-      </c>
+        <v>924</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天6</t>
+          <t>化神前期·周天5</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>3819</v>
+        <v>3804</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>31</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>930</v>
-      </c>
+        <v>961</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天7</t>
+          <t>化神前期·周天6</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>3834</v>
+        <v>3819</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>31</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>899</v>
-      </c>
+        <v>930</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天8</t>
+          <t>化神前期·周天7</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>3846</v>
+        <v>3834</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>940</v>
-      </c>
+        <v>899</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>化神前期·周天9</t>
+          <t>化神前期·周天8</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>3861</v>
+        <v>3846</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>30</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>910</v>
-      </c>
+        <v>940</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>化神前期·周天9</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>3861</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>化神前期·周天10</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n">
+      <c r="B111" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="C110" s="3" t="n">
+      <c r="C111" s="3" t="n">
         <v>3876</v>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="D111" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="E110" s="3" t="n">
+      <c r="E111" s="3" t="n">
         <v>954</v>
       </c>
+      <c r="F111" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
